--- a/data/availability/projects/horizon-egypt-developments/saada-boutique.xlsx
+++ b/data/availability/projects/horizon-egypt-developments/saada-boutique.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1159,7 +1159,6 @@
       <c r="G2" t="n">
         <v>71</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1170,7 +1169,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1216,7 +1215,6 @@
       <c r="G3" t="n">
         <v>105</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1227,7 +1225,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1273,7 +1271,6 @@
       <c r="G4" t="n">
         <v>134</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1284,7 +1281,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1330,7 +1327,6 @@
       <c r="G5" t="n">
         <v>175</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1341,7 +1337,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1387,7 +1383,6 @@
       <c r="G6" t="n">
         <v>175</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1398,7 +1393,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1444,7 +1439,6 @@
       <c r="G7" t="n">
         <v>215</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1455,7 +1449,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1501,7 +1495,6 @@
       <c r="G8" t="n">
         <v>215</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1512,7 +1505,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1558,7 +1551,6 @@
       <c r="G9" t="n">
         <v>210</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1569,7 +1561,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1615,7 +1607,6 @@
       <c r="G10" t="n">
         <v>285</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1626,7 +1617,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1672,7 +1663,6 @@
       <c r="G11" t="n">
         <v>315</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1683,7 +1673,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1729,7 +1719,6 @@
       <c r="G12" t="n">
         <v>278</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1740,7 +1729,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1786,7 +1775,6 @@
       <c r="G13" t="n">
         <v>380</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Lagoon &amp; Greenery</t>
@@ -1797,7 +1785,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
